--- a/TestData/TS25_ValidateAllContracts.xlsx
+++ b/TestData/TS25_ValidateAllContracts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34589C0-6AE5-4D5E-AF24-FB103E5AED5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F96B299-CC76-4C6E-8C96-F01FC6059D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="11376" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -55,9 +55,6 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Dealership &amp; Rental Services</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -284,6 +281,9 @@
   </si>
   <si>
     <t>10</t>
+  </si>
+  <si>
+    <t>CSDN-0000001546</t>
   </si>
 </sst>
 </file>
@@ -327,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -335,6 +335,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -663,337 +666,337 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="T1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="X1" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="AA1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AB1" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="AD1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N2" t="s">
+        <v>82</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="P2" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="U2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="W2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="X2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Y2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Z2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AD2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
       <c r="G3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" t="s">
+        <v>25</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" t="s">
+        <v>28</v>
+      </c>
+      <c r="V3" t="s">
+        <v>57</v>
+      </c>
+      <c r="W3" t="s">
+        <v>31</v>
+      </c>
+      <c r="X3" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y3" t="s">
         <v>64</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" t="s">
-        <v>26</v>
-      </c>
-      <c r="S3" t="s">
-        <v>26</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="U3" t="s">
-        <v>29</v>
-      </c>
-      <c r="V3" t="s">
-        <v>58</v>
-      </c>
-      <c r="W3" t="s">
-        <v>32</v>
-      </c>
-      <c r="X3" t="s">
-        <v>34</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>65</v>
-      </c>
       <c r="Z3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" t="s">
         <v>8</v>
       </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
       <c r="G4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R4" t="s">
+        <v>25</v>
+      </c>
+      <c r="S4" t="s">
+        <v>25</v>
+      </c>
+      <c r="T4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="P4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="R4" t="s">
-        <v>26</v>
-      </c>
-      <c r="S4" t="s">
-        <v>26</v>
-      </c>
-      <c r="T4" s="3" t="s">
-        <v>38</v>
-      </c>
       <c r="U4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="V4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="W4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="X4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Y4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AA4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1013,28 +1016,28 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1054,10 +1057,10 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -1066,24 +1069,24 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" t="s">
         <v>75</v>
       </c>
-      <c r="B2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>76</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>77</v>
-      </c>
-      <c r="E2" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1107,54 +1110,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1175,24 +1178,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" t="s">
         <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TS25_ValidateAllContracts.xlsx
+++ b/TestData/TS25_ValidateAllContracts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F96B299-CC76-4C6E-8C96-F01FC6059D91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FAFC55-15FF-4E95-A9C1-0B93186D6746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -241,9 +241,6 @@
     <t>DRC - Ad Valorem Services</t>
   </si>
   <si>
-    <t>Debt Capital Markets</t>
-  </si>
-  <si>
     <t>IG</t>
   </si>
   <si>
@@ -284,6 +281,9 @@
   </si>
   <si>
     <t>CSDN-0000001546</t>
+  </si>
+  <si>
+    <t>James Craven</t>
   </si>
 </sst>
 </file>
@@ -729,7 +729,7 @@
         <v>46</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.3">
@@ -740,13 +740,13 @@
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -773,16 +773,16 @@
         <v>17</v>
       </c>
       <c r="N2" t="s">
+        <v>81</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="P2" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="R2" t="s">
         <v>25</v>
@@ -812,13 +812,13 @@
         <v>42</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AD2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.3">
@@ -835,7 +835,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F3" t="s">
         <v>8</v>
@@ -924,7 +924,7 @@
         <v>7</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -996,7 +996,7 @@
         <v>36</v>
       </c>
       <c r="AD4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1019,15 +1019,15 @@
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1057,10 +1057,10 @@
   <sheetData>
     <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>4</v>
@@ -1074,19 +1074,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C2" t="s">
         <v>74</v>
       </c>
-      <c r="B2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>75</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>76</v>
-      </c>
-      <c r="E2" t="s">
-        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/TS25_ValidateAllContracts.xlsx
+++ b/TestData/TS25_ValidateAllContracts.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2FAFC55-15FF-4E95-A9C1-0B93186D6746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744FB145-162D-4B20-86DC-E444DDE43EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="86">
   <si>
     <t>Client</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>James Craven</t>
+  </si>
+  <si>
+    <t>Dental</t>
   </si>
 </sst>
 </file>
@@ -743,10 +746,10 @@
         <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>83</v>
+        <v>71</v>
+      </c>
+      <c r="E2" t="s">
+        <v>85</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
